--- a/data/trans_dic/IP31KM09_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM09_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,26; 98,56</t>
+          <t>88,37; 96,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,43; 96,44</t>
+          <t>92,73; 98,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91,19; 96,53</t>
+          <t>91,66; 96,77</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,26; 94,43</t>
+          <t>91,2; 98,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,92; 98,54</t>
+          <t>83,96; 94,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,3; 95,75</t>
+          <t>89,34; 95,97</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,27; 97,82</t>
+          <t>92,05; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>93,35; 100,0</t>
+          <t>86,29; 97,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,84; 98,4</t>
+          <t>92,7; 98,37</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,25; 97,09</t>
+          <t>89,29; 96,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,97; 96,55</t>
+          <t>90,3; 96,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,74; 95,99</t>
+          <t>90,69; 95,55</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>85,19; 94,16</t>
+          <t>69,55; 94,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,09; 94,21</t>
+          <t>85,43; 94,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,8; 92,55</t>
+          <t>76,06; 92,84</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82,02; 95,42</t>
+          <t>87,26; 97,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88,35; 98,07</t>
+          <t>82,83; 95,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88,24; 95,67</t>
+          <t>87,42; 95,62</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>91,02; 94,46</t>
+          <t>88,56; 94,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,78; 94,77</t>
+          <t>90,82; 94,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,82; 94,25</t>
+          <t>90,53; 94,12</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>146</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>98063</t>
+          <t>112734</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>125962</t>
+          <t>96856</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224026</t>
+          <t>209590</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93839; 100246</t>
+          <t>107112; 116355</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>119532; 130363</t>
+          <t>93051; 99004</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>216023; 228671</t>
+          <t>203087; 214396</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>124</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>84044</t>
+          <t>86781</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90050</t>
+          <t>86055</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174094</t>
+          <t>172836</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77761; 88193</t>
+          <t>81971; 88812</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84267; 92338</t>
+          <t>80103; 90197</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167086; 179152</t>
+          <t>165534; 177826</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47123</t>
+          <t>54700</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61002</t>
+          <t>49110</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>108124</t>
+          <t>103810</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43715; 48999</t>
+          <t>51406; 55844</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58187; 62334</t>
+          <t>44879; 50900</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103251; 110628</t>
+          <t>99984; 106091</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>253</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>204042</t>
+          <t>184135</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>199062</t>
+          <t>165384</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>403105</t>
+          <t>349518</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>196671; 209272</t>
+          <t>176181; 189760</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>191324; 205312</t>
+          <t>159503; 169890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>392824; 411031</t>
+          <t>339152; 357305</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>153</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>104122</t>
+          <t>127417</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>137890</t>
+          <t>104409</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>231826</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>98398; 108758</t>
+          <t>101257; 137597</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>102203; 150228</t>
+          <t>98647; 108674</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>202918; 254486</t>
+          <t>198558; 242362</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>90</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>62499</t>
+          <t>61987</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>65276</t>
+          <t>63794</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>127774</t>
+          <t>125782</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56508; 65737</t>
+          <t>57475; 64317</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60987; 67697</t>
+          <t>58278; 67400</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>121709; 131955</t>
+          <t>119090; 130248</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>832</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>599893</t>
+          <t>627754</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>679242</t>
+          <t>565608</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1279135</t>
+          <t>1193363</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>587187; 609379</t>
+          <t>598363; 641425</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>635581; 694082</t>
+          <t>554235; 575051</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1237294; 1298228</t>
+          <t>1164107; 1210315</t>
         </is>
       </c>
     </row>
